--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487153_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487153_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6474</v>
+        <v>5.3936</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1808</v>
+        <v>5.7395</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5333</v>
+        <v>-0.3459</v>
       </c>
       <c r="G2" t="n">
         <v>3.6777</v>
@@ -610,13 +610,13 @@
         <v>1.158</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1977</v>
+        <v>-0.0562</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8144</v>
+        <v>0.3731</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6167</v>
+        <v>-0.4293</v>
       </c>
       <c r="V2" t="n">
         <v>0.614</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. AZANZA TERUEL</t>
+          <t>H. OREJA ELSO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4681</v>
+        <v>1.451</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0902</v>
+        <v>1.6963</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5583</v>
+        <v>-0.2453</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1344</v>
+        <v>1.4334</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8653</v>
+        <v>-0.8393</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9996</v>
+        <v>2.2727</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1478</v>
+        <v>1.9343</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5848</v>
+        <v>0.0621</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7326</v>
+        <v>1.8722</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0134</v>
+        <v>-0.5009</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2805</v>
+        <v>-0.9014</v>
       </c>
       <c r="O3" t="n">
-        <v>0.267</v>
+        <v>0.4006</v>
       </c>
       <c r="P3" t="n">
         <v>0.579</v>
@@ -688,28 +688,28 @@
         <v>0.579</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0985</v>
+        <v>-0.193</v>
       </c>
       <c r="T3" t="n">
         <v>-0.238</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3364</v>
+        <v>0.0449</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6562</v>
+        <v>-0.3684</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6562</v>
+        <v>-0.3684</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. OREJA ELSO</t>
+          <t>G. AZANZA TERUEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.225</v>
+        <v>1.3808</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5773</v>
+        <v>0.01</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3524</v>
+        <v>1.3709</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4334</v>
+        <v>0.1344</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8393</v>
+        <v>-0.8653</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2727</v>
+        <v>0.9996</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9343</v>
+        <v>0.1478</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0621</v>
+        <v>-0.5848</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8722</v>
+        <v>0.7326</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5009</v>
+        <v>-0.0134</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9014</v>
+        <v>-0.2805</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4006</v>
+        <v>0.267</v>
       </c>
       <c r="P4" t="n">
         <v>0.579</v>
@@ -766,22 +766,22 @@
         <v>0.579</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4191</v>
+        <v>0.0112</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3569</v>
+        <v>-0.1378</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0621</v>
+        <v>0.149</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3684</v>
+        <v>0.6562</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3684</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.5566</v>
+        <v>-1.043</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7159</v>
+        <v>-0.2559</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8406</v>
+        <v>-0.7871</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9601</v>
@@ -844,13 +844,13 @@
         <v>0.965</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9439</v>
+        <v>-0.4303</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4019</v>
+        <v>0.0582</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.542</v>
+        <v>-0.4885</v>
       </c>
       <c r="V5" t="n">
         <v>1.3125</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9665</v>
+        <v>-1.6859</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0407</v>
+        <v>0.241</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0071</v>
+        <v>-1.9268</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3653</v>
@@ -922,13 +922,13 @@
         <v>1.158</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.852</v>
+        <v>-0.5714</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5354</v>
+        <v>-0.3351</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3166</v>
+        <v>-0.2363</v>
       </c>
       <c r="V6" t="n">
         <v>-0.9421</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.1304</v>
+        <v>-3.0799</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2897</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.4202</v>
+        <v>-3.6076</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9445</v>
@@ -1000,13 +1000,13 @@
         <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3616</v>
+        <v>-0.311</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5949</v>
+        <v>-0.3569</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2333</v>
+        <v>0.0459</v>
       </c>
       <c r="V7" t="n">
         <v>-1.5964</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2283</v>
+        <v>-3.3284</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.583</v>
+        <v>-0.6832</v>
       </c>
       <c r="F8" t="n">
         <v>-2.6453</v>
@@ -1078,10 +1078,10 @@
         <v>1.3511</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.505</v>
+        <v>-0.6051</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1652</v>
+        <v>-0.2654</v>
       </c>
       <c r="U8" t="n">
         <v>-0.3398</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1826</v>
+        <v>-3.9178</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7742</v>
+        <v>1.0121</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.9567</v>
+        <v>-4.93</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7173</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1547</v>
+        <v>-0.89</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8328</v>
+        <v>-0.5949</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3219</v>
+        <v>-0.2952</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3105</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3888</v>
+        <v>-4.3303</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3502</v>
+        <v>-3.372</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0386</v>
+        <v>-0.9583</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9028</v>
@@ -1234,13 +1234,13 @@
         <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2162</v>
+        <v>0.2746</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2062</v>
+        <v>0.1844</v>
       </c>
       <c r="U10" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0902</v>
       </c>
       <c r="V10" t="n">
         <v>0.614</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1942</v>
+        <v>-4.7956</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2136</v>
+        <v>-0.9756</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.9806</v>
+        <v>-3.82</v>
       </c>
       <c r="G11" t="n">
         <v>-6.2192</v>
@@ -1312,13 +1312,13 @@
         <v>0.965</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1699</v>
+        <v>-0.7714</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6398</v>
+        <v>-0.4019</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5301</v>
+        <v>-0.3695</v>
       </c>
       <c r="V11" t="n">
         <v>1.2299</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5908</v>
+        <v>-5.4004</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7311</v>
+        <v>-3.1927</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8596</v>
+        <v>-2.2076</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4012</v>
@@ -1390,13 +1390,13 @@
         <v>1.3511</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4977</v>
+        <v>-0.3074</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8778</v>
+        <v>-0.3394</v>
       </c>
       <c r="U12" t="n">
-        <v>0.38</v>
+        <v>0.032</v>
       </c>
       <c r="V12" t="n">
         <v>0.8173</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.5695</v>
+        <v>-6.6241</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3953</v>
+        <v>-3.4766</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.1743</v>
+        <v>-3.1475</v>
       </c>
       <c r="G13" t="n">
         <v>-2.5728</v>
@@ -1468,13 +1468,13 @@
         <v>2.1231</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7687</v>
+        <v>-0.8233</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4032</v>
+        <v>-0.4845</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3656</v>
+        <v>-0.3388</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4559</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.4672</v>
+        <v>-25.98</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.216600000000001</v>
+        <v>-2.7294</v>
       </c>
       <c r="F14" t="n">
-        <v>-23.2504</v>
+        <v>-23.2505</v>
       </c>
       <c r="G14" t="n">
         <v>-16.982</v>
@@ -1546,16 +1546,16 @@
         <v>12.5453</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.1602</v>
+        <v>-4.673299999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.025300000000001</v>
+        <v>-2.5382</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.1352</v>
+        <v>-2.1354</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.429400000000001</v>
+        <v>-1.4294</v>
       </c>
       <c r="W14" t="n">
         <v>5.071099999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.6097</v>
+        <v>8.4438</v>
       </c>
       <c r="E15" t="n">
-        <v>8.8406</v>
+        <v>8.1396</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2308</v>
+        <v>0.3042</v>
       </c>
       <c r="G15" t="n">
         <v>3.9501</v>
@@ -1624,13 +1624,13 @@
         <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6669</v>
+        <v>0.501</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8884</v>
+        <v>0.1874</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2214</v>
+        <v>0.3136</v>
       </c>
       <c r="V15" t="n">
         <v>3.0277</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.5252</v>
+        <v>7.173</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1943</v>
+        <v>7.757</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3309</v>
+        <v>-0.584</v>
       </c>
       <c r="G16" t="n">
-        <v>3.7339</v>
+        <v>6.8582</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2513</v>
+        <v>2.9932</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4826</v>
+        <v>3.865</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1561</v>
+        <v>8.5532</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9341</v>
+        <v>3.9949</v>
       </c>
       <c r="L16" t="n">
-        <v>2.222</v>
+        <v>4.5583</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4222</v>
+        <v>-1.6951</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6828</v>
+        <v>-1.0018</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2606</v>
+        <v>-0.6933</v>
       </c>
       <c r="P16" t="n">
-        <v>0.193</v>
+        <v>-0.772</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9301</v>
+        <v>-2.1231</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1231</v>
+        <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3703</v>
+        <v>0.1448</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7403</v>
+        <v>0.0988</v>
       </c>
       <c r="U16" t="n">
-        <v>1.63</v>
+        <v>0.0459</v>
       </c>
       <c r="V16" t="n">
-        <v>1.228</v>
+        <v>0.9421</v>
       </c>
       <c r="W16" t="n">
         <v>1.228</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.4049</v>
+        <v>6.5357</v>
       </c>
       <c r="E17" t="n">
-        <v>7.2563</v>
+        <v>4.7937</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8512999999999999</v>
+        <v>1.742</v>
       </c>
       <c r="G17" t="n">
-        <v>6.8582</v>
+        <v>3.7339</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9932</v>
+        <v>1.2513</v>
       </c>
       <c r="I17" t="n">
-        <v>3.865</v>
+        <v>2.4826</v>
       </c>
       <c r="J17" t="n">
-        <v>8.5532</v>
+        <v>5.1561</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9949</v>
+        <v>2.9341</v>
       </c>
       <c r="L17" t="n">
-        <v>4.5583</v>
+        <v>2.222</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6951</v>
+        <v>-1.4222</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0018</v>
+        <v>-1.6828</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6933</v>
+        <v>0.2606</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.772</v>
+        <v>0.193</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1231</v>
+        <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3511</v>
+        <v>2.1231</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6233</v>
+        <v>1.3808</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4019</v>
+        <v>0.3398</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2214</v>
+        <v>1.041</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9421</v>
+        <v>1.228</v>
       </c>
       <c r="W17" t="n">
         <v>1.228</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.4082</v>
+        <v>4.0413</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4735</v>
+        <v>2.9728</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9347</v>
+        <v>1.0685</v>
       </c>
       <c r="G18" t="n">
         <v>3.3672</v>
@@ -1858,13 +1858,13 @@
         <v>1.5441</v>
       </c>
       <c r="S18" t="n">
-        <v>1.246</v>
+        <v>0.8791</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7549</v>
+        <v>0.2542</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4911</v>
+        <v>0.6249</v>
       </c>
       <c r="V18" t="n">
         <v>-1.5561</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.888</v>
+        <v>3.2521</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2271</v>
+        <v>2.127</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6608</v>
+        <v>1.1251</v>
       </c>
       <c r="G19" t="n">
         <v>2.0593</v>
@@ -1936,13 +1936,13 @@
         <v>0.965</v>
       </c>
       <c r="S19" t="n">
-        <v>1.427</v>
+        <v>0.7912</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3993</v>
+        <v>0.2991</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0278</v>
+        <v>0.4921</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3704</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PEREZ BENITO</t>
+          <t>I. BETOLAZA BELOKI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1831</v>
+        <v>2.4845</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2967</v>
+        <v>2.8925</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8864</v>
+        <v>-0.408</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3702</v>
+        <v>1.4272</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5276</v>
+        <v>0.5775</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1574</v>
+        <v>0.8497</v>
       </c>
       <c r="J20" t="n">
-        <v>0.498</v>
+        <v>3.7963</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2588</v>
+        <v>1.7128</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7569</v>
+        <v>2.0835</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8682</v>
+        <v>-2.3691</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2688</v>
+        <v>-1.1353</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4006</v>
+        <v>-1.2338</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.193</v>
+        <v>0.193</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1231</v>
+        <v>-1.158</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9301</v>
+        <v>1.3511</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5183</v>
+        <v>0.8642</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4079</v>
+        <v>0.2542</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1104</v>
+        <v>0.6101</v>
       </c>
       <c r="V20" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. BETOLAZA BELOKI</t>
+          <t>J. PEREZ BENITO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.0234</v>
+        <v>1.6695</v>
       </c>
       <c r="E21" t="n">
-        <v>2.592</v>
+        <v>0.5957</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5686</v>
+        <v>1.0737</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4272</v>
+        <v>-0.3702</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5775</v>
+        <v>-1.5276</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8497</v>
+        <v>1.1574</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7963</v>
+        <v>0.498</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7128</v>
+        <v>-0.2588</v>
       </c>
       <c r="L21" t="n">
-        <v>2.0835</v>
+        <v>0.7569</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3691</v>
+        <v>-0.8682</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1353</v>
+        <v>-1.2688</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2338</v>
+        <v>0.4006</v>
       </c>
       <c r="P21" t="n">
-        <v>0.193</v>
+        <v>-0.193</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.158</v>
+        <v>-2.1231</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3511</v>
+        <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4032</v>
+        <v>1.0047</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0462</v>
+        <v>0.7069</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4495</v>
+        <v>0.2978</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0275</v>
+        <v>0.6137</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1071</v>
+        <v>-0.7065</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0796</v>
+        <v>1.3202</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0989</v>
@@ -2170,13 +2170,13 @@
         <v>1.5441</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5076000000000001</v>
+        <v>0.1335</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3569</v>
+        <v>0.0436</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1507</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1717</v>
+        <v>0.289</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7346</v>
+        <v>-1.4341</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5629</v>
+        <v>1.7232</v>
       </c>
       <c r="G23" t="n">
         <v>1.0498</v>
@@ -2248,13 +2248,13 @@
         <v>1.7371</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2637</v>
+        <v>0.197</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3278</v>
+        <v>-0.0274</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0641</v>
+        <v>0.2244</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5717</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.9079</v>
+        <v>-0.9684</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6948</v>
+        <v>-0.5947</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2131</v>
+        <v>-0.3737</v>
       </c>
       <c r="G24" t="n">
         <v>0.0743</v>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1758</v>
+        <v>0.1153</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1785</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3543</v>
+        <v>0.1937</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.7976</v>
+        <v>-1.3703</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.6301</v>
+        <v>-2.2295</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8325</v>
+        <v>0.8593</v>
       </c>
       <c r="G25" t="n">
         <v>-2.5452</v>
@@ -2404,13 +2404,13 @@
         <v>0.772</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0178</v>
+        <v>0.4452</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4164</v>
+        <v>-0.0159</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4343</v>
+        <v>0.461</v>
       </c>
       <c r="V25" t="n">
         <v>-0.0422</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.6707</v>
+        <v>-4.0292</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.4633</v>
+        <v>-1.0628</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.2074</v>
+        <v>-2.9664</v>
       </c>
       <c r="G26" t="n">
         <v>-2.5234</v>
@@ -2482,13 +2482,13 @@
         <v>0.965</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2703</v>
+        <v>0.3711</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3278</v>
+        <v>0.0727</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0575</v>
+        <v>0.2984</v>
       </c>
       <c r="V26" t="n">
         <v>-2.4559</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>27.4671</v>
+        <v>28.1347</v>
       </c>
       <c r="E27" t="n">
-        <v>23.2506</v>
+        <v>23.2507</v>
       </c>
       <c r="F27" t="n">
-        <v>4.216600000000001</v>
+        <v>4.884100000000001</v>
       </c>
       <c r="G27" t="n">
         <v>16.9823</v>
@@ -2548,7 +2548,7 @@
         <v>-10.0176</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.1607000000000001</v>
+        <v>-0.1606999999999999</v>
       </c>
       <c r="P27" t="n">
         <v>2.895099999999999</v>
@@ -2560,13 +2560,13 @@
         <v>15.4407</v>
       </c>
       <c r="S27" t="n">
-        <v>6.1604</v>
+        <v>6.8279</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1353</v>
+        <v>2.1351</v>
       </c>
       <c r="U27" t="n">
-        <v>4.025499999999999</v>
+        <v>4.6928</v>
       </c>
       <c r="V27" t="n">
         <v>1.4295</v>
